--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_28-06-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_28-06-2025.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>£16.70</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>£17.48</t>
+          <t>Error: list index out of range</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>£959.7</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /165mm_celotex_xr4000.html (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000002C1F46DE190&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>£1,225.00</t>
+          <t>Error: HTTPSConnectionPool(host='insulation4less.co.uk', port=443): Max retries exceeded with url: /products/thermaclass-cavity-wall-21?variant=39698151342133 (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x000002C1F60071D0&gt;, 'Connection to insulation4less.co.uk timed out. (connect timeout=None)'))</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
